--- a/data/3.meta_data/basic_info/26_03_01_basic_info.xlsx
+++ b/data/3.meta_data/basic_info/26_03_01_basic_info.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AE2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -518,6 +518,138 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2">
+        <v>46082</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0100a</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>10.1177/00222194261417592</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>University Students With Specific Learning Disabilities: Do Soft Skills and Study-Related Factors Make a Difference to Their Academic Outcomes?</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Understanding the role of individual factors associated with positive academic outcomes is fundamental to providing effective support for students with specific learning disabilities (SLDs) throughout their academic careers. The present study aimed to investigate group differences between students with and without SLDs and to examine the relationships between study-related factors, social, emotional, and behavioral (SEB) skills, and student outcomes (achievement, academic and life satisfaction, and burnout) in a sample of 752 university students (133 male</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>JOURNAL OF LEARNING DISABILITIES</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pellegrino, Gerardo and Feraco, Tommaso and De Vita, Francesca and Martino, Maria Grazia and Matteucci, Maria Cristina and Montesano, Lorena and Passolunghi, Maria Chiara and Re, Anna Maria and Sini, Barbara and Tinti, Carla and Valenti, Antonella and Meneghetti, Chiara and Carretti, Barbara</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Pellegrino et al.</t>
+        </is>
+      </c>
+      <c r="K2">
+        <v>2026</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>academicachievement; schoolsatisfaction; disabilities</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>gerardo.pellegrino@phd.unipd.it</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>https://osf.io/69q84/</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="T2">
+        <v>82</v>
+      </c>
+      <c r="U2">
+        <v>22.28</v>
+      </c>
+      <c r="V2">
+        <v>752</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>young_adult</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>clinical</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>learning disabilities</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>bessi45</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/3.meta_data/basic_info/26_03_01_basic_info.xlsx
+++ b/data/3.meta_data/basic_info/26_03_01_basic_info.xlsx
@@ -1,22 +1,189 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_EC74FDCE8F79A89360642C52EA7272372213866F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+  <si>
+    <t>download_date</t>
+  </si>
+  <si>
+    <t>paper_id</t>
+  </si>
+  <si>
+    <t>sample_id</t>
+  </si>
+  <si>
+    <t>matrix_id</t>
+  </si>
+  <si>
+    <t>doi</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>abstract</t>
+  </si>
+  <si>
+    <t>journal</t>
+  </si>
+  <si>
+    <t>authors</t>
+  </si>
+  <si>
+    <t>author_et_al</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>exclusion_general</t>
+  </si>
+  <si>
+    <t>exclusion_meta</t>
+  </si>
+  <si>
+    <t>review_topics</t>
+  </si>
+  <si>
+    <t>final_decision</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>open_data</t>
+  </si>
+  <si>
+    <t>study_design</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>age_class</t>
+  </si>
+  <si>
+    <t>clinical</t>
+  </si>
+  <si>
+    <t>clinical_spec</t>
+  </si>
+  <si>
+    <t>seb_measure</t>
+  </si>
+  <si>
+    <t>seb_measure_type</t>
+  </si>
+  <si>
+    <t>trait_frame</t>
+  </si>
+  <si>
+    <t>coder</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>additional</t>
+  </si>
+  <si>
+    <t>0100</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>0100a</t>
+  </si>
+  <si>
+    <t>10.1177/00222194261417592</t>
+  </si>
+  <si>
+    <t>University Students With Specific Learning Disabilities: Do Soft Skills and Study-Related Factors Make a Difference to Their Academic Outcomes?</t>
+  </si>
+  <si>
+    <t>Understanding the role of individual factors associated with positive academic outcomes is fundamental to providing effective support for students with specific learning disabilities (SLDs) throughout their academic careers. The present study aimed to investigate group differences between students with and without SLDs and to examine the relationships between study-related factors, social, emotional, and behavioral (SEB) skills, and student outcomes (achievement, academic and life satisfaction, and burnout) in a sample of 752 university students (133 male</t>
+  </si>
+  <si>
+    <t>JOURNAL OF LEARNING DISABILITIES</t>
+  </si>
+  <si>
+    <t>Pellegrino, Gerardo and Feraco, Tommaso and De Vita, Francesca and Martino, Maria Grazia and Matteucci, Maria Cristina and Montesano, Lorena and Passolunghi, Maria Chiara and Re, Anna Maria and Sini, Barbara and Tinti, Carla and Valenti, Antonella and Meneghetti, Chiara and Carretti, Barbara</t>
+  </si>
+  <si>
+    <t>Pellegrino et al.</t>
+  </si>
+  <si>
+    <t>include</t>
+  </si>
+  <si>
+    <t>academicachievement; schoolsatisfaction; disabilities</t>
+  </si>
+  <si>
+    <t>both</t>
+  </si>
+  <si>
+    <t>gerardo.pellegrino@phd.unipd.it</t>
+  </si>
+  <si>
+    <t>https://osf.io/69q84/</t>
+  </si>
+  <si>
+    <t>cross</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>young_adult</t>
+  </si>
+  <si>
+    <t>learning disabilities</t>
+  </si>
+  <si>
+    <t>bessi45</t>
+  </si>
+  <si>
+    <t>short</t>
+  </si>
+  <si>
+    <t>TF</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd HH:mm:ss UTC"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss\ \U\T\C"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,17 +230,25 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -111,7 +286,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -145,6 +320,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -179,9 +355,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -354,261 +531,165 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>download_date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>paper_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sample_id</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>matrix_id</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>doi</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>abstract</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>authors</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>author_et_al</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>exclusion_general</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>exclusion_meta</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>review_topics</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>final_decision</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>open_data</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>study_design</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>gender</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>age_class</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>clinical</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>clinical_spec</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>seb_measure</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>seb_measure_type</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>trait_frame</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>coder</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>additional</t>
-        </is>
+    <row r="1" spans="1:31" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:31">
       <c r="A2" s="2">
         <v>46082</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0100</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0100a</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>10.1177/00222194261417592</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>University Students With Specific Learning Disabilities: Do Soft Skills and Study-Related Factors Make a Difference to Their Academic Outcomes?</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Understanding the role of individual factors associated with positive academic outcomes is fundamental to providing effective support for students with specific learning disabilities (SLDs) throughout their academic careers. The present study aimed to investigate group differences between students with and without SLDs and to examine the relationships between study-related factors, social, emotional, and behavioral (SEB) skills, and student outcomes (achievement, academic and life satisfaction, and burnout) in a sample of 752 university students (133 male</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>JOURNAL OF LEARNING DISABILITIES</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Pellegrino, Gerardo and Feraco, Tommaso and De Vita, Francesca and Martino, Maria Grazia and Matteucci, Maria Cristina and Montesano, Lorena and Passolunghi, Maria Chiara and Re, Anna Maria and Sini, Barbara and Tinti, Carla and Valenti, Antonella and Meneghetti, Chiara and Carretti, Barbara</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Pellegrino et al.</t>
-        </is>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" t="s">
+        <v>39</v>
       </c>
       <c r="K2">
         <v>2026</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>include</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>include</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>academicachievement; schoolsatisfaction; disabilities</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>gerardo.pellegrino@phd.unipd.it</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>https://osf.io/69q84/</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>cross</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
+      <c r="L2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" t="s">
+        <v>46</v>
       </c>
       <c r="T2">
         <v>82</v>
@@ -619,35 +700,23 @@
       <c r="V2">
         <v>752</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>young_adult</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>clinical</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>learning disabilities</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>bessi45</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>TF</t>
-        </is>
+      <c r="W2" t="s">
+        <v>47</v>
+      </c>
+      <c r="X2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/data/3.meta_data/basic_info/26_03_01_basic_info.xlsx
+++ b/data/3.meta_data/basic_info/26_03_01_basic_info.xlsx
@@ -582,7 +582,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>academicachievement; schoolsatisfaction; disabilities</t>
+          <t>academicachievement; schoolsatisfaction; learningdisabilities</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
